--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -1974,7 +1974,7 @@
         <v>100</v>
       </c>
       <c r="C24" s="26">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="D24" s="26">
         <v>8</v>
@@ -2004,7 +2004,7 @@
         <v>100</v>
       </c>
       <c r="C25" s="26">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="D25" s="26">
         <v>8</v>

--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -1798,7 +1798,7 @@
         <v>100</v>
       </c>
       <c r="C18" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D18" s="34">
         <v>90</v>
@@ -1827,7 +1827,7 @@
         <v>100</v>
       </c>
       <c r="C19" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D19" s="34">
         <v>90</v>
@@ -1856,7 +1856,7 @@
         <v>100</v>
       </c>
       <c r="C20" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D20" s="34">
         <v>90</v>
@@ -1886,7 +1886,7 @@
         <v>100</v>
       </c>
       <c r="C21" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D21" s="34">
         <v>50</v>

--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="203">
   <si>
     <t>CARMELITAS BARILOCHE WEB</t>
   </si>
@@ -383,6 +383,9 @@
     <t>cerámica pesebre</t>
   </si>
   <si>
+    <t>Pesebre artesanal - Diseños exclusivos. 14x9,5 cm</t>
+  </si>
+  <si>
     <t>..\..\Pictures\A TRABAJOS WEB\Cerámica\PESEBRES\Pesebre cerámica.jpg</t>
   </si>
   <si>
@@ -566,7 +569,70 @@
     <t>Nuestra Señora de las Nieves, imagen realizada en Cerámica con base de madera, 26,5 alto x 9,5 x 9,5. Advocación muy querida de todos, es también Patrona de nuestra Diócesis de Bariloche.</t>
   </si>
   <si>
-    <t>Pesebre artesanal - Diseños exclusivos. 13x7,5 cm</t>
+    <t>LITÚRGICOS-SACERDOTALES</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de telar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casulla con Estolón de telar </t>
+  </si>
+  <si>
+    <t>casullavioleta</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de tela-Bordadas</t>
+  </si>
+  <si>
+    <t>estolatelar-1-</t>
+  </si>
+  <si>
+    <t>estolabordada-1-</t>
+  </si>
+  <si>
+    <t>..\..\..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-1-.jpg</t>
+  </si>
+  <si>
+    <t>Corte y confección  propia con hermosos diseños bordados a máquina. Todos los colores litúrgicos.</t>
+  </si>
+  <si>
+    <t>Confeccionada en su totalidad con telar artesanal. De fina lana con diseños exclusivos. Todos los colores litúrgicos.v (12 cm de ancho x 165 cm de largo)</t>
+  </si>
+  <si>
+    <t>estolabordada-2-</t>
+  </si>
+  <si>
+    <t>estolabordada-3-</t>
+  </si>
+  <si>
+    <t>estolabordada-4-</t>
+  </si>
+  <si>
+    <t>Cíngulo</t>
+  </si>
+  <si>
+    <t>Confeccionado a mano con hilo macramé. 2,90 mt largo</t>
+  </si>
+  <si>
+    <t>..\..\..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolabordada-1-.jpg</t>
+  </si>
+  <si>
+    <t>..\..\..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolabordada-2-.jpg</t>
+  </si>
+  <si>
+    <t>..\..\..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolabordada-3-.jpg</t>
+  </si>
+  <si>
+    <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\cíngulo-1-.jpg</t>
+  </si>
+  <si>
+    <t>Corte y confección  propia con hermosos diseños bordados a máquina. Todos los colores litúrgicos. 1,45 mt de largo x 14 cm de ancho</t>
+  </si>
+  <si>
+    <t>Muy cómoda y amplia (1,23 mt de largo x 1,46 de ancho) Adornada con estolón confeccionado en telar artesanal. .  Incluye la Casulla con  Estola.</t>
+  </si>
+  <si>
+    <t>cíngulo-1-</t>
   </si>
 </sst>
 </file>
@@ -628,7 +694,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -692,6 +758,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,7 +914,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -978,7 +1056,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
@@ -986,7 +1063,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1015,6 +1091,33 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1282,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.85546875" style="1" customWidth="1"/>
@@ -1296,14 +1399,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
       <c r="G1" s="4"/>
       <c r="H1" s="5"/>
       <c r="L1" s="4"/>
@@ -1376,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="15">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="D4" s="15">
         <v>20</v>
@@ -1406,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="15">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="D5" s="15">
         <v>90</v>
@@ -1436,7 +1539,7 @@
         <v>100</v>
       </c>
       <c r="C6" s="26">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D6" s="26">
         <v>1</v>
@@ -1465,8 +1568,8 @@
       <c r="B7" s="25">
         <v>100</v>
       </c>
-      <c r="C7" s="26">
-        <v>2000</v>
+      <c r="C7" s="29">
+        <v>1500</v>
       </c>
       <c r="D7" s="29">
         <v>1</v>
@@ -1496,7 +1599,7 @@
         <v>100</v>
       </c>
       <c r="C8" s="26">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="D8" s="26">
         <v>2</v>
@@ -1526,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="26">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D9" s="26">
         <v>1</v>
@@ -1557,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="26">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D10" s="26">
         <v>1</v>
@@ -1588,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="26">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D11" s="26">
         <v>1</v>
@@ -1619,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="26">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D12" s="26">
         <v>1</v>
@@ -1650,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="26">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D13" s="26">
         <v>1</v>
@@ -1798,7 +1901,7 @@
         <v>100</v>
       </c>
       <c r="C18" s="34">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="D18" s="34">
         <v>90</v>
@@ -1827,7 +1930,7 @@
         <v>100</v>
       </c>
       <c r="C19" s="34">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="D19" s="34">
         <v>90</v>
@@ -1856,7 +1959,7 @@
         <v>100</v>
       </c>
       <c r="C20" s="34">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="D20" s="34">
         <v>90</v>
@@ -1886,7 +1989,7 @@
         <v>100</v>
       </c>
       <c r="C21" s="34">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="D21" s="34">
         <v>50</v>
@@ -1974,7 +2077,7 @@
         <v>100</v>
       </c>
       <c r="C24" s="26">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="D24" s="26">
         <v>8</v>
@@ -2004,7 +2107,7 @@
         <v>100</v>
       </c>
       <c r="C25" s="26">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="D25" s="26">
         <v>8</v>
@@ -2092,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="54">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="D28" s="54">
         <v>40</v>
@@ -2121,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="54">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="D29" s="54">
         <v>35</v>
@@ -2162,10 +2265,10 @@
         <v>118</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>180</v>
+        <v>119</v>
       </c>
       <c r="H30" s="57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I30" s="59"/>
       <c r="J30" s="60"/>
@@ -2174,7 +2277,7 @@
     </row>
     <row r="31" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="52" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="53">
         <v>1</v>
@@ -2189,13 +2292,13 @@
         <v>109</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="81" t="s">
-        <v>178</v>
+        <v>122</v>
+      </c>
+      <c r="H31" s="79" t="s">
+        <v>179</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="11"/>
@@ -2203,7 +2306,7 @@
     </row>
     <row r="32" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" s="53">
         <v>1</v>
@@ -2218,13 +2321,13 @@
         <v>109</v>
       </c>
       <c r="F32" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="G32" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="H32" s="78" t="s">
         <v>176</v>
-      </c>
-      <c r="G32" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32" s="80" t="s">
-        <v>175</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="11"/>
@@ -2232,7 +2335,7 @@
     </row>
     <row r="33" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="52" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B33" s="53">
         <v>1</v>
@@ -2244,16 +2347,16 @@
         <v>18</v>
       </c>
       <c r="E33" s="58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G33" s="62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H33" s="57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="11"/>
@@ -2261,7 +2364,7 @@
     </row>
     <row r="34" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="53">
         <v>1</v>
@@ -2273,16 +2376,16 @@
         <v>18</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G34" s="62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H34" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="19"/>
@@ -2290,7 +2393,7 @@
     </row>
     <row r="35" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="53">
         <v>1</v>
@@ -2302,16 +2405,16 @@
         <v>18</v>
       </c>
       <c r="E35" s="58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F35" s="52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G35" s="62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H35" s="57" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="10"/>
@@ -2319,7 +2422,7 @@
     </row>
     <row r="36" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="53">
         <v>1</v>
@@ -2331,16 +2434,16 @@
         <v>18</v>
       </c>
       <c r="E36" s="58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F36" s="52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G36" s="62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H36" s="63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="48"/>
       <c r="J36" s="11"/>
@@ -2349,268 +2452,457 @@
     </row>
     <row r="37" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="64">
         <v>100</v>
       </c>
-      <c r="C37" s="65">
+      <c r="C37" s="96">
         <v>12000</v>
       </c>
-      <c r="D37" s="66">
+      <c r="D37" s="65">
         <v>350</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="H37" s="68" t="s">
+      <c r="G37" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="I37" s="69"/>
+      <c r="H37" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="I37" s="68"/>
     </row>
     <row r="38" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="70" t="s">
-        <v>140</v>
+      <c r="A38" s="69" t="s">
+        <v>141</v>
       </c>
       <c r="B38" s="64">
         <v>100</v>
       </c>
-      <c r="C38" s="71">
+      <c r="C38" s="97">
         <v>8000</v>
       </c>
-      <c r="D38" s="66">
+      <c r="D38" s="65">
         <v>20</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="G38" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="H38" s="73" t="s">
+      <c r="G38" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="I38" s="74"/>
+      <c r="H38" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38" s="72"/>
     </row>
     <row r="39" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="64">
         <v>100</v>
       </c>
-      <c r="C39" s="66">
+      <c r="C39" s="97">
         <v>8000</v>
       </c>
-      <c r="D39" s="66">
+      <c r="D39" s="65">
         <v>20</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="H39" s="75" t="s">
+        <v>146</v>
+      </c>
+      <c r="G39" s="70" t="s">
         <v>143</v>
       </c>
+      <c r="H39" s="73" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="40" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="76" t="s">
-        <v>146</v>
-      </c>
-      <c r="B40" s="77">
-        <v>1</v>
-      </c>
-      <c r="C40" s="78">
-        <v>15000</v>
-      </c>
-      <c r="D40" s="78">
+      <c r="A40" s="74" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="75">
+        <v>1</v>
+      </c>
+      <c r="C40" s="98">
+        <v>10000</v>
+      </c>
+      <c r="D40" s="76">
         <v>125</v>
       </c>
       <c r="E40" s="58" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="G40" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="77" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="74" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="75">
+        <v>1</v>
+      </c>
+      <c r="C41" s="98">
+        <v>10000</v>
+      </c>
+      <c r="D41" s="76">
+        <v>125</v>
+      </c>
+      <c r="E41" s="58" t="s">
         <v>148</v>
       </c>
-      <c r="G40" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="H40" s="79" t="s">
+      <c r="F41" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="58" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="76" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="77">
-        <v>1</v>
-      </c>
-      <c r="C41" s="78">
-        <v>15000</v>
-      </c>
-      <c r="D41" s="78">
-        <v>125</v>
-      </c>
-      <c r="E41" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="F41" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="G41" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="H41" s="79" t="s">
-        <v>153</v>
+      <c r="H41" s="77" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="82" t="s">
-        <v>154</v>
-      </c>
-      <c r="B42" s="83">
-        <v>1</v>
-      </c>
-      <c r="C42" s="84">
+      <c r="A42" s="80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" s="81">
+        <v>1</v>
+      </c>
+      <c r="C42" s="99">
         <v>10000</v>
       </c>
-      <c r="D42" s="84">
+      <c r="D42" s="82">
         <v>40</v>
       </c>
-      <c r="E42" s="85" t="s">
-        <v>155</v>
-      </c>
-      <c r="F42" s="85" t="s">
+      <c r="E42" s="83" t="s">
         <v>156</v>
       </c>
-      <c r="G42" s="85" t="s">
+      <c r="F42" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="H42" s="86" t="s">
+      <c r="G42" s="83" t="s">
         <v>158</v>
       </c>
+      <c r="H42" s="84" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="43" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="87" t="s">
-        <v>159</v>
-      </c>
-      <c r="B43" s="83">
-        <v>1</v>
-      </c>
-      <c r="C43" s="84">
+      <c r="A43" s="85" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" s="81">
+        <v>1</v>
+      </c>
+      <c r="C43" s="99">
         <v>10000</v>
       </c>
-      <c r="D43" s="84">
+      <c r="D43" s="82">
         <v>40</v>
       </c>
-      <c r="E43" s="85" t="s">
-        <v>155</v>
-      </c>
-      <c r="F43" s="85" t="s">
-        <v>160</v>
-      </c>
-      <c r="G43" s="85" t="s">
-        <v>157</v>
-      </c>
-      <c r="H43" s="86" t="s">
+      <c r="E43" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="83" t="s">
         <v>161</v>
       </c>
+      <c r="G43" s="83" t="s">
+        <v>158</v>
+      </c>
+      <c r="H43" s="84" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="44" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="87" t="s">
-        <v>162</v>
-      </c>
-      <c r="B44" s="83">
-        <v>1</v>
-      </c>
-      <c r="C44" s="84">
+      <c r="A44" s="85" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" s="81">
+        <v>1</v>
+      </c>
+      <c r="C44" s="99">
         <v>10000</v>
       </c>
-      <c r="D44" s="84">
+      <c r="D44" s="82">
         <v>40</v>
       </c>
-      <c r="E44" s="85" t="s">
-        <v>155</v>
-      </c>
-      <c r="F44" s="85" t="s">
-        <v>163</v>
-      </c>
-      <c r="G44" s="85" t="s">
-        <v>157</v>
-      </c>
-      <c r="H44" s="86" t="s">
+      <c r="E44" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="F44" s="83" t="s">
         <v>164</v>
       </c>
+      <c r="G44" s="83" t="s">
+        <v>158</v>
+      </c>
+      <c r="H44" s="84" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="45" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="87" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="83">
-        <v>1</v>
-      </c>
-      <c r="C45" s="84">
+      <c r="A45" s="85" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" s="81">
+        <v>1</v>
+      </c>
+      <c r="C45" s="99">
         <v>10000</v>
       </c>
-      <c r="D45" s="84">
+      <c r="D45" s="82">
         <v>40</v>
       </c>
-      <c r="E45" s="85" t="s">
-        <v>155</v>
-      </c>
-      <c r="F45" s="85" t="s">
-        <v>166</v>
-      </c>
-      <c r="G45" s="85" t="s">
-        <v>157</v>
-      </c>
-      <c r="H45" s="86" t="s">
+      <c r="E45" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="F45" s="83" t="s">
         <v>167</v>
       </c>
+      <c r="G45" s="83" t="s">
+        <v>158</v>
+      </c>
+      <c r="H45" s="84" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="46" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="88" t="s">
-        <v>168</v>
-      </c>
-      <c r="B46" s="89">
+      <c r="A46" s="86" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="87">
         <v>100</v>
       </c>
-      <c r="C46" s="90">
+      <c r="C46" s="100">
         <v>8000</v>
       </c>
-      <c r="D46" s="90">
+      <c r="D46" s="88">
         <v>250</v>
       </c>
-      <c r="E46" s="91" t="s">
-        <v>169</v>
-      </c>
-      <c r="F46" s="91" t="s">
+      <c r="E46" s="89" t="s">
         <v>170</v>
       </c>
-      <c r="G46" s="91" t="s">
+      <c r="F46" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="H46" s="92" t="s">
+      <c r="G46" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="I46" s="93" t="s">
+      <c r="H46" s="90" t="s">
         <v>173</v>
       </c>
+      <c r="I46" s="91" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="86" t="s">
+        <v>194</v>
+      </c>
+      <c r="B47" s="87">
+        <v>1</v>
+      </c>
+      <c r="C47" s="100">
+        <v>35000</v>
+      </c>
+      <c r="D47" s="88">
+        <v>60</v>
+      </c>
+      <c r="E47" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="F47" s="89" t="s">
+        <v>202</v>
+      </c>
+      <c r="G47" s="89" t="s">
+        <v>195</v>
+      </c>
+      <c r="H47" s="78" t="s">
+        <v>199</v>
+      </c>
+      <c r="I47" s="91"/>
+    </row>
+    <row r="48" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="95" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="94">
+        <v>1</v>
+      </c>
+      <c r="C48" s="101">
+        <v>80000</v>
+      </c>
+      <c r="D48" s="93">
+        <v>140</v>
+      </c>
+      <c r="E48" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F48" s="92" t="s">
+        <v>186</v>
+      </c>
+      <c r="G48" s="92" t="s">
+        <v>190</v>
+      </c>
+      <c r="H48" s="104" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="94">
+        <v>10</v>
+      </c>
+      <c r="C49" s="101">
+        <v>60000</v>
+      </c>
+      <c r="D49" s="3">
+        <v>200</v>
+      </c>
+      <c r="E49" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F49" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="92" t="s">
+        <v>200</v>
+      </c>
+      <c r="H49" s="78" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="94">
+        <v>10</v>
+      </c>
+      <c r="C50" s="101">
+        <v>60000</v>
+      </c>
+      <c r="D50" s="3">
+        <v>200</v>
+      </c>
+      <c r="E50" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F50" s="92" t="s">
+        <v>191</v>
+      </c>
+      <c r="G50" s="92" t="s">
+        <v>189</v>
+      </c>
+      <c r="H50" s="78" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="94">
+        <v>10</v>
+      </c>
+      <c r="C51" s="101">
+        <v>60000</v>
+      </c>
+      <c r="D51" s="3">
+        <v>200</v>
+      </c>
+      <c r="E51" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F51" s="92" t="s">
+        <v>192</v>
+      </c>
+      <c r="G51" s="92" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="78" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="95" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="94">
+        <v>0</v>
+      </c>
+      <c r="C52" s="101">
+        <v>60000</v>
+      </c>
+      <c r="D52" s="93">
+        <v>200</v>
+      </c>
+      <c r="E52" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="92" t="s">
+        <v>193</v>
+      </c>
+      <c r="G52" s="92" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="92"/>
+    </row>
+    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="95" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="94">
+        <v>0</v>
+      </c>
+      <c r="C53" s="101">
+        <v>200000</v>
+      </c>
+      <c r="D53" s="93">
+        <v>1200</v>
+      </c>
+      <c r="E53" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F53" s="92" t="s">
+        <v>184</v>
+      </c>
+      <c r="G53" s="92" t="s">
+        <v>201</v>
+      </c>
+      <c r="H53" s="92"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="103"/>
+      <c r="B54" s="94"/>
+      <c r="C54" s="101"/>
+      <c r="D54" s="93"/>
+      <c r="E54" s="103"/>
+      <c r="F54" s="103"/>
+      <c r="G54" s="102"/>
+      <c r="H54" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2657,11 +2949,16 @@
     <hyperlink ref="H43" r:id="rId38"/>
     <hyperlink ref="H44" r:id="rId39"/>
     <hyperlink ref="H45" r:id="rId40"/>
-    <hyperlink ref="H46" r:id="rId41"/>
-    <hyperlink ref="H32" r:id="rId42"/>
-    <hyperlink ref="H31" r:id="rId43"/>
+    <hyperlink ref="H32" r:id="rId41"/>
+    <hyperlink ref="H31" r:id="rId42"/>
+    <hyperlink ref="H48" r:id="rId43"/>
+    <hyperlink ref="H49" r:id="rId44"/>
+    <hyperlink ref="H50" r:id="rId45"/>
+    <hyperlink ref="H51" r:id="rId46"/>
+    <hyperlink ref="H47" r:id="rId47"/>
+    <hyperlink ref="H46" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.39374999999999999" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId44"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId49"/>
 </worksheet>
 </file>
--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -1479,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="15">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="D4" s="15">
         <v>20</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="15">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="D5" s="15">
         <v>90</v>
@@ -1539,7 +1539,7 @@
         <v>100</v>
       </c>
       <c r="C6" s="26">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D6" s="26">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         <v>100</v>
       </c>
       <c r="C7" s="29">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="29">
         <v>1</v>
@@ -1599,7 +1599,7 @@
         <v>100</v>
       </c>
       <c r="C8" s="26">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D8" s="26">
         <v>2</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="26">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D9" s="26">
         <v>1</v>
@@ -1660,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="26">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D10" s="26">
         <v>1</v>
@@ -1691,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="26">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D11" s="26">
         <v>1</v>
@@ -1722,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="26">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D12" s="26">
         <v>1</v>
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="26">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D13" s="26">
         <v>1</v>
@@ -1901,7 +1901,7 @@
         <v>100</v>
       </c>
       <c r="C18" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D18" s="34">
         <v>90</v>
@@ -1930,7 +1930,7 @@
         <v>100</v>
       </c>
       <c r="C19" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D19" s="34">
         <v>90</v>
@@ -1959,7 +1959,7 @@
         <v>100</v>
       </c>
       <c r="C20" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D20" s="34">
         <v>90</v>
@@ -1989,7 +1989,7 @@
         <v>100</v>
       </c>
       <c r="C21" s="34">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="D21" s="34">
         <v>50</v>
@@ -2077,7 +2077,7 @@
         <v>100</v>
       </c>
       <c r="C24" s="26">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D24" s="26">
         <v>8</v>
@@ -2107,7 +2107,7 @@
         <v>100</v>
       </c>
       <c r="C25" s="26">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="D25" s="26">
         <v>8</v>
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="54">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="D28" s="54">
         <v>40</v>
@@ -2224,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="54">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="D29" s="54">
         <v>35</v>
@@ -2538,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="98">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="D40" s="76">
         <v>125</v>
@@ -2564,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="98">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="D41" s="76">
         <v>125</v>

--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="206">
   <si>
     <t>CARMELITAS BARILOCHE WEB</t>
   </si>
@@ -581,9 +581,6 @@
     <t>casullavioleta</t>
   </si>
   <si>
-    <t>Estola Sacerdotal de tela-Bordadas</t>
-  </si>
-  <si>
     <t>estolatelar-1-</t>
   </si>
   <si>
@@ -633,6 +630,18 @@
   </si>
   <si>
     <t>cíngulo-1-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de tela--1-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de tela-Bordadas-2-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de tela-Bordadas-3-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de tela-Bordadas-4-</t>
   </si>
 </sst>
 </file>
@@ -914,7 +923,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -1118,6 +1127,9 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1399,14 +1411,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
       <c r="G1" s="4"/>
       <c r="H1" s="5"/>
       <c r="L1" s="4"/>
@@ -2458,7 +2470,7 @@
         <v>100</v>
       </c>
       <c r="C37" s="96">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="D37" s="65">
         <v>350</v>
@@ -2717,7 +2729,7 @@
     </row>
     <row r="47" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="86" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B47" s="87">
         <v>1</v>
@@ -2732,13 +2744,13 @@
         <v>181</v>
       </c>
       <c r="F47" s="89" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G47" s="89" t="s">
-        <v>195</v>
-      </c>
-      <c r="H47" s="78" t="s">
-        <v>199</v>
+        <v>194</v>
+      </c>
+      <c r="H47" s="107" t="s">
+        <v>198</v>
       </c>
       <c r="I47" s="91"/>
     </row>
@@ -2759,18 +2771,18 @@
         <v>181</v>
       </c>
       <c r="F48" s="92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G48" s="92" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H48" s="104" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="95" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B49" s="94">
         <v>10</v>
@@ -2778,25 +2790,25 @@
       <c r="C49" s="101">
         <v>60000</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="105">
         <v>200</v>
       </c>
       <c r="E49" s="92" t="s">
         <v>181</v>
       </c>
       <c r="F49" s="92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G49" s="92" t="s">
-        <v>200</v>
-      </c>
-      <c r="H49" s="78" t="s">
-        <v>196</v>
+        <v>199</v>
+      </c>
+      <c r="H49" s="107" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="95" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B50" s="94">
         <v>10</v>
@@ -2804,25 +2816,25 @@
       <c r="C50" s="101">
         <v>60000</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="106">
         <v>200</v>
       </c>
       <c r="E50" s="92" t="s">
         <v>181</v>
       </c>
       <c r="F50" s="92" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G50" s="92" t="s">
-        <v>189</v>
-      </c>
-      <c r="H50" s="78" t="s">
-        <v>197</v>
+        <v>188</v>
+      </c>
+      <c r="H50" s="107" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="95" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B51" s="94">
         <v>10</v>
@@ -2830,25 +2842,25 @@
       <c r="C51" s="101">
         <v>60000</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="105">
         <v>200</v>
       </c>
       <c r="E51" s="92" t="s">
         <v>181</v>
       </c>
       <c r="F51" s="92" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G51" s="92" t="s">
-        <v>189</v>
-      </c>
-      <c r="H51" s="78" t="s">
-        <v>198</v>
+        <v>188</v>
+      </c>
+      <c r="H51" s="107" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="95" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="B52" s="94">
         <v>0</v>
@@ -2863,10 +2875,10 @@
         <v>181</v>
       </c>
       <c r="F52" s="92" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G52" s="92" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H52" s="92"/>
     </row>
@@ -2890,7 +2902,7 @@
         <v>184</v>
       </c>
       <c r="G53" s="92" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H53" s="92"/>
     </row>

--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="212">
   <si>
     <t>CARMELITAS BARILOCHE WEB</t>
   </si>
@@ -572,9 +572,6 @@
     <t>LITÚRGICOS-SACERDOTALES</t>
   </si>
   <si>
-    <t>Estola Sacerdotal de telar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Casulla con Estolón de telar </t>
   </si>
   <si>
@@ -632,9 +629,6 @@
     <t>cíngulo-1-</t>
   </si>
   <si>
-    <t>Estola Sacerdotal de tela--1-</t>
-  </si>
-  <si>
     <t>Estola Sacerdotal de tela-Bordadas-2-</t>
   </si>
   <si>
@@ -642,6 +636,30 @@
   </si>
   <si>
     <t>Estola Sacerdotal de tela-Bordadas-4-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de telar-1-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de telar-2-</t>
+  </si>
+  <si>
+    <t>estolatelar-2-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de tela-Bordadas-1-</t>
+  </si>
+  <si>
+    <t>estolatelar-3-</t>
+  </si>
+  <si>
+    <t>Estola Sacerdotal de telar-3-</t>
+  </si>
+  <si>
+    <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-2-.jpeg</t>
+  </si>
+  <si>
+    <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-3-.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.85546875" style="1" customWidth="1"/>
@@ -2729,7 +2747,7 @@
     </row>
     <row r="47" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B47" s="87">
         <v>1</v>
@@ -2744,19 +2762,19 @@
         <v>181</v>
       </c>
       <c r="F47" s="89" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G47" s="89" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H47" s="107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I47" s="91"/>
     </row>
     <row r="48" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="95" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="B48" s="94">
         <v>1</v>
@@ -2771,70 +2789,70 @@
         <v>181</v>
       </c>
       <c r="F48" s="92" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G48" s="92" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H48" s="104" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="95" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B49" s="94">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C49" s="101">
-        <v>60000</v>
-      </c>
-      <c r="D49" s="105">
-        <v>200</v>
+        <v>80000</v>
+      </c>
+      <c r="D49" s="93">
+        <v>140</v>
       </c>
       <c r="E49" s="92" t="s">
         <v>181</v>
       </c>
       <c r="F49" s="92" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="G49" s="92" t="s">
-        <v>199</v>
-      </c>
-      <c r="H49" s="107" t="s">
-        <v>195</v>
+        <v>188</v>
+      </c>
+      <c r="H49" s="78" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="95" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B50" s="94">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C50" s="101">
-        <v>60000</v>
-      </c>
-      <c r="D50" s="106">
-        <v>200</v>
+        <v>80000</v>
+      </c>
+      <c r="D50" s="93">
+        <v>140</v>
       </c>
       <c r="E50" s="92" t="s">
         <v>181</v>
       </c>
       <c r="F50" s="92" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="G50" s="92" t="s">
         <v>188</v>
       </c>
-      <c r="H50" s="107" t="s">
-        <v>196</v>
+      <c r="H50" s="78" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="95" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B51" s="94">
         <v>10</v>
@@ -2849,72 +2867,124 @@
         <v>181</v>
       </c>
       <c r="F51" s="92" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G51" s="92" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H51" s="107" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="95" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B52" s="94">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C52" s="101">
         <v>60000</v>
       </c>
-      <c r="D52" s="93">
+      <c r="D52" s="106">
         <v>200</v>
       </c>
       <c r="E52" s="92" t="s">
         <v>181</v>
       </c>
       <c r="F52" s="92" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G52" s="92" t="s">
-        <v>188</v>
-      </c>
-      <c r="H52" s="92"/>
+        <v>187</v>
+      </c>
+      <c r="H52" s="107" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="95" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B53" s="94">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C53" s="101">
-        <v>200000</v>
-      </c>
-      <c r="D53" s="93">
-        <v>1200</v>
+        <v>60000</v>
+      </c>
+      <c r="D53" s="105">
+        <v>200</v>
       </c>
       <c r="E53" s="92" t="s">
         <v>181</v>
       </c>
       <c r="F53" s="92" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G53" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="H53" s="107" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="95" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="94">
+        <v>0</v>
+      </c>
+      <c r="C54" s="101">
+        <v>60000</v>
+      </c>
+      <c r="D54" s="93">
         <v>200</v>
       </c>
-      <c r="H53" s="92"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="103"/>
-      <c r="B54" s="94"/>
-      <c r="C54" s="101"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="103"/>
-      <c r="F54" s="103"/>
-      <c r="G54" s="102"/>
-      <c r="H54" s="102"/>
+      <c r="E54" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F54" s="92" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" s="92"/>
+    </row>
+    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="95" t="s">
+        <v>182</v>
+      </c>
+      <c r="B55" s="94">
+        <v>0</v>
+      </c>
+      <c r="C55" s="101">
+        <v>200000</v>
+      </c>
+      <c r="D55" s="93">
+        <v>1200</v>
+      </c>
+      <c r="E55" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="F55" s="92" t="s">
+        <v>183</v>
+      </c>
+      <c r="G55" s="92" t="s">
+        <v>199</v>
+      </c>
+      <c r="H55" s="92"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="103"/>
+      <c r="B56" s="94"/>
+      <c r="C56" s="101"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="103"/>
+      <c r="F56" s="103"/>
+      <c r="G56" s="102"/>
+      <c r="H56" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2964,13 +3034,15 @@
     <hyperlink ref="H32" r:id="rId41"/>
     <hyperlink ref="H31" r:id="rId42"/>
     <hyperlink ref="H48" r:id="rId43"/>
-    <hyperlink ref="H49" r:id="rId44"/>
-    <hyperlink ref="H50" r:id="rId45"/>
-    <hyperlink ref="H51" r:id="rId46"/>
+    <hyperlink ref="H51" r:id="rId44"/>
+    <hyperlink ref="H52" r:id="rId45"/>
+    <hyperlink ref="H53" r:id="rId46"/>
     <hyperlink ref="H47" r:id="rId47"/>
     <hyperlink ref="H46" r:id="rId48"/>
+    <hyperlink ref="H49" r:id="rId49"/>
+    <hyperlink ref="H50" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.39374999999999999" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId49"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId51"/>
 </worksheet>
 </file>
--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="217">
   <si>
     <t>CARMELITAS BARILOCHE WEB</t>
   </si>
@@ -660,6 +660,21 @@
   </si>
   <si>
     <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-3-.jpeg</t>
+  </si>
+  <si>
+    <t>VARIOS&gt;HONGOS SECOS</t>
+  </si>
+  <si>
+    <t>hongossecos</t>
+  </si>
+  <si>
+    <t>Hongos de Pino - SUILLUS LAKEI - Deshidratados de manera natural,  sin conservantes. Recolección  realizada en nuestro bosque de manera ecológica. Ideales para salsas con carne, rissotto, etc</t>
+  </si>
+  <si>
+    <t>..\Pictures\A TRABAJOS WEB\VARIOS\hongossecos.jpeg</t>
+  </si>
+  <si>
+    <t>Hongos secos</t>
   </si>
 </sst>
 </file>
@@ -721,7 +736,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -797,6 +812,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -941,7 +962,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -1148,9 +1169,14 @@
     <xf numFmtId="1" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="2" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Explanatory Text" xfId="3"/>
@@ -1415,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.85546875" style="1" customWidth="1"/>
@@ -1429,14 +1455,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
       <c r="G1" s="4"/>
       <c r="H1" s="5"/>
       <c r="L1" s="4"/>
@@ -2820,7 +2846,7 @@
       <c r="G49" s="92" t="s">
         <v>188</v>
       </c>
-      <c r="H49" s="78" t="s">
+      <c r="H49" s="108" t="s">
         <v>210</v>
       </c>
     </row>
@@ -2846,7 +2872,7 @@
       <c r="G50" s="92" t="s">
         <v>188</v>
       </c>
-      <c r="H50" s="78" t="s">
+      <c r="H50" s="108" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2985,6 +3011,29 @@
       <c r="F56" s="103"/>
       <c r="G56" s="102"/>
       <c r="H56" s="102"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="111" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" s="2">
+        <v>100</v>
+      </c>
+      <c r="C57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E57" s="110" t="s">
+        <v>212</v>
+      </c>
+      <c r="F57" s="110" t="s">
+        <v>213</v>
+      </c>
+      <c r="G57" s="113" t="s">
+        <v>214</v>
+      </c>
+      <c r="H57" s="112" t="s">
+        <v>215</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3041,8 +3090,9 @@
     <hyperlink ref="H46" r:id="rId48"/>
     <hyperlink ref="H49" r:id="rId49"/>
     <hyperlink ref="H50" r:id="rId50"/>
+    <hyperlink ref="H57" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.39374999999999999" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId51"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId52"/>
 </worksheet>
 </file>
--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -1170,13 +1170,13 @@
     <xf numFmtId="1" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="2" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Explanatory Text" xfId="3"/>
@@ -1455,14 +1455,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
       <c r="G1" s="4"/>
       <c r="H1" s="5"/>
       <c r="L1" s="4"/>
@@ -3013,7 +3013,7 @@
       <c r="H56" s="102"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="111" t="s">
+      <c r="A57" s="110" t="s">
         <v>216</v>
       </c>
       <c r="B57" s="2">
@@ -3022,16 +3022,19 @@
       <c r="C57" s="3">
         <v>6000</v>
       </c>
-      <c r="E57" s="110" t="s">
+      <c r="D57" s="3">
+        <v>50</v>
+      </c>
+      <c r="E57" s="109" t="s">
         <v>212</v>
       </c>
-      <c r="F57" s="110" t="s">
+      <c r="F57" s="109" t="s">
         <v>213</v>
       </c>
-      <c r="G57" s="113" t="s">
+      <c r="G57" s="112" t="s">
         <v>214</v>
       </c>
-      <c r="H57" s="112" t="s">
+      <c r="H57" s="111" t="s">
         <v>215</v>
       </c>
     </row>

--- a/data/web-repositorio.xlsx
+++ b/data/web-repositorio.xlsx
@@ -656,12 +656,6 @@
     <t>Estola Sacerdotal de telar-3-</t>
   </si>
   <si>
-    <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-2-.jpeg</t>
-  </si>
-  <si>
-    <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-3-.jpeg</t>
-  </si>
-  <si>
     <t>VARIOS&gt;HONGOS SECOS</t>
   </si>
   <si>
@@ -671,10 +665,16 @@
     <t>Hongos de Pino - SUILLUS LAKEI - Deshidratados de manera natural,  sin conservantes. Recolección  realizada en nuestro bosque de manera ecológica. Ideales para salsas con carne, rissotto, etc</t>
   </si>
   <si>
-    <t>..\Pictures\A TRABAJOS WEB\VARIOS\hongossecos.jpeg</t>
-  </si>
-  <si>
     <t>Hongos secos</t>
+  </si>
+  <si>
+    <t>..\Pictures\A TRABAJOS WEB\VARIOS\hongossecos.jpg</t>
+  </si>
+  <si>
+    <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-2-.jpg</t>
+  </si>
+  <si>
+    <t>..\Pictures\A TRABAJOS WEB\Litúrgicos-Sacerdotales\estolatelar-3-.jpg</t>
   </si>
 </sst>
 </file>
@@ -736,7 +736,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -812,12 +812,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1169,14 +1163,14 @@
     <xf numFmtId="1" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="2" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="2" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Explanatory Text" xfId="3"/>
@@ -1455,14 +1449,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
       <c r="G1" s="4"/>
       <c r="H1" s="5"/>
       <c r="L1" s="4"/>
@@ -2846,8 +2840,8 @@
       <c r="G49" s="92" t="s">
         <v>188</v>
       </c>
-      <c r="H49" s="108" t="s">
-        <v>210</v>
+      <c r="H49" s="113" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2872,8 +2866,8 @@
       <c r="G50" s="92" t="s">
         <v>188</v>
       </c>
-      <c r="H50" s="108" t="s">
-        <v>211</v>
+      <c r="H50" s="113" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3013,8 +3007,8 @@
       <c r="H56" s="102"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="110" t="s">
-        <v>216</v>
+      <c r="A57" s="109" t="s">
+        <v>213</v>
       </c>
       <c r="B57" s="2">
         <v>100</v>
@@ -3025,17 +3019,17 @@
       <c r="D57" s="3">
         <v>50</v>
       </c>
-      <c r="E57" s="109" t="s">
+      <c r="E57" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="F57" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="G57" s="110" t="s">
         <v>212</v>
       </c>
-      <c r="F57" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="G57" s="112" t="s">
+      <c r="H57" s="112" t="s">
         <v>214</v>
-      </c>
-      <c r="H57" s="111" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3091,9 +3085,9 @@
     <hyperlink ref="H53" r:id="rId46"/>
     <hyperlink ref="H47" r:id="rId47"/>
     <hyperlink ref="H46" r:id="rId48"/>
-    <hyperlink ref="H49" r:id="rId49"/>
-    <hyperlink ref="H50" r:id="rId50"/>
-    <hyperlink ref="H57" r:id="rId51"/>
+    <hyperlink ref="H57" r:id="rId49"/>
+    <hyperlink ref="H49" r:id="rId50"/>
+    <hyperlink ref="H50" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.39374999999999999" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId52"/>
